--- a/data/config/luban/config/general/red_dot.xlsx
+++ b/data/config/luban/config/general/red_dot.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="14250" windowHeight="7545"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -30,30 +30,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>##var</t>
   </si>
   <si>
-    <t>item_template_id</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>item_type</t>
-  </si>
-  <si>
-    <t>stacked</t>
-  </si>
-  <si>
-    <t>squares</t>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>parent_node_id</t>
+  </si>
+  <si>
+    <t>red_dot_status_type</t>
+  </si>
+  <si>
+    <t>save_database</t>
   </si>
   <si>
     <t>##type</t>
   </si>
   <si>
-    <t>int</t>
+    <t>red_dot_type</t>
+  </si>
+  <si>
+    <t>string</t>
   </si>
   <si>
     <t>bool</t>
@@ -62,13 +65,19 @@
     <t>##</t>
   </si>
   <si>
-    <t>物品编号</t>
-  </si>
-  <si>
-    <t>物品名称</t>
-  </si>
-  <si>
-    <t>物品类型</t>
+    <t>红点类型</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>父节点id</t>
+  </si>
+  <si>
+    <t>红点状态类型</t>
+  </si>
+  <si>
+    <t>是否保存数据库</t>
   </si>
   <si>
     <t>金币</t>
@@ -1297,39 +1306,54 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:6">
       <c r="B4" s="2">
-        <v>10001</v>
+        <v>10000</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D4" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1337,19 +1361,22 @@
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D3">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
+  <conditionalFormatting sqref="B4">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B3 B5:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
+  <conditionalFormatting sqref="B1:B3 B6:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="90"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
